--- a/output/Data and Chart Outputs/us_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/us_power_capacity.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -839,7 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -854,7 +854,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -941,7 +940,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -970,7 +969,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -999,7 +998,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1028,7 +1027,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1057,7 +1056,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1086,7 +1085,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1115,7 +1114,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1144,7 +1143,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1173,7 +1172,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1202,7 +1201,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1231,7 +1230,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1260,7 +1259,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1289,7 +1288,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1318,7 +1317,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1347,7 +1346,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1376,7 +1375,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1405,7 +1404,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1434,7 +1433,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1463,7 +1462,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1492,7 +1491,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1521,7 +1520,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1550,7 +1549,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1579,7 +1578,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1608,7 +1607,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1637,7 +1636,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1666,7 +1665,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1695,7 +1694,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1724,7 +1723,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1753,7 +1752,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1782,7 +1781,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1811,7 +1810,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1840,7 +1839,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1869,7 +1868,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1898,7 +1897,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1927,7 +1926,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1956,7 +1955,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1985,7 +1984,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2014,7 +2013,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2043,7 +2042,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2072,7 +2071,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2101,7 +2100,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2130,7 +2129,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2159,7 +2158,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2188,7 +2187,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2217,7 +2216,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2246,7 +2245,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2275,7 +2274,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2304,7 +2303,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2333,7 +2332,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2362,7 +2361,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2391,7 +2390,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2420,7 +2419,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2449,7 +2448,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2478,7 +2477,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2507,7 +2506,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2536,7 +2535,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2565,7 +2564,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2594,7 +2593,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2623,7 +2622,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2652,7 +2651,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2681,7 +2680,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2710,7 +2709,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2739,7 +2738,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2768,7 +2767,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2797,7 +2796,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2826,7 +2825,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2855,7 +2854,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">

--- a/output/Data and Chart Outputs/us_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/us_power_capacity.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -840,6 +839,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -854,6 +854,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -940,7 +941,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -969,7 +970,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -998,7 +999,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1027,7 +1028,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1056,7 +1057,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1085,7 +1086,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1114,7 +1115,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1143,7 +1144,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1172,7 +1173,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1201,7 +1202,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1230,7 +1231,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1259,7 +1260,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1288,7 +1289,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1317,7 +1318,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1346,7 +1347,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1375,7 +1376,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1404,7 +1405,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1433,7 +1434,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1462,7 +1463,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1491,7 +1492,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1520,7 +1521,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1549,7 +1550,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1578,7 +1579,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1607,7 +1608,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1636,7 +1637,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1665,7 +1666,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1694,7 +1695,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1723,7 +1724,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1752,7 +1753,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1781,7 +1782,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1810,7 +1811,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1839,7 +1840,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1868,7 +1869,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1897,7 +1898,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1926,7 +1927,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1955,7 +1956,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1984,7 +1985,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2013,7 +2014,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2042,7 +2043,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2071,7 +2072,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2100,7 +2101,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2129,7 +2130,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2158,7 +2159,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2187,7 +2188,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2216,7 +2217,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2245,7 +2246,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2274,7 +2275,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2303,7 +2304,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2332,7 +2333,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2361,7 +2362,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2390,7 +2391,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2419,7 +2420,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2448,7 +2449,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2477,7 +2478,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2506,7 +2507,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2535,7 +2536,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2564,7 +2565,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2593,7 +2594,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2622,7 +2623,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2651,7 +2652,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2680,7 +2681,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2709,7 +2710,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2738,7 +2739,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2767,7 +2768,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2796,7 +2797,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2825,7 +2826,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2854,7 +2855,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">

--- a/output/Data and Chart Outputs/us_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/us_power_capacity.xlsx
@@ -45,8 +45,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -86,12 +86,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -180,6 +181,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>US installed generating capacity (EIA-860M, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -201,7 +203,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -229,7 +231,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -285,7 +287,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -313,7 +315,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -341,7 +343,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -369,7 +371,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -511,6 +513,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Southern installed generating capacity (EIA-860M by balancing authority, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -532,7 +535,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -560,7 +563,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -588,7 +591,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -644,7 +647,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -672,7 +675,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -842,6 +845,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>TVA installed generating capacity (EIA-860M by balancing authority, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -863,7 +867,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -891,7 +895,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -919,7 +923,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -947,7 +951,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -975,7 +979,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1003,7 +1007,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1031,7 +1035,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1173,6 +1177,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Gas-fired fleet capacity factor (EIA-930 gas generation / EIA-860M gas capacity) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -1565,6 +1570,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>MISO gas-fired fleet capacity factor (EIA-930 / EIA-860M) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -1701,6 +1707,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>ERCOT gas-fired fleet capacity factor (EIA-930 / EIA-860M) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -1837,6 +1844,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Lower 48 installed generating capacity (EIA-860M by balancing authority, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -1858,7 +1866,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1886,7 +1894,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1942,7 +1950,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1970,7 +1978,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1998,7 +2006,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2026,7 +2034,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2168,6 +2176,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>ERCOT installed generating capacity (EIA-860M by balancing authority, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -2189,7 +2198,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2217,7 +2226,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2245,7 +2254,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2273,7 +2282,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2301,7 +2310,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2357,7 +2366,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2499,6 +2508,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>PJM installed generating capacity (EIA-860M by balancing authority, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -2520,7 +2530,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2548,7 +2558,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2576,7 +2586,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2604,7 +2614,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2632,7 +2642,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2660,7 +2670,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2830,6 +2840,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>MISO installed generating capacity (EIA-860M by balancing authority, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -2851,7 +2862,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2879,7 +2890,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2935,7 +2946,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2963,7 +2974,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2991,7 +3002,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3161,6 +3172,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>SPP installed generating capacity (EIA-860M by balancing authority, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -3182,7 +3194,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3210,7 +3222,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3238,7 +3250,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3266,7 +3278,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3294,7 +3306,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3322,7 +3334,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3350,7 +3362,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3492,6 +3504,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>CAISO installed generating capacity (EIA-860M by balancing authority, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -3513,7 +3526,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3541,7 +3554,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3569,7 +3582,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3597,7 +3610,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3625,7 +3638,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3823,6 +3836,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>NYISO installed generating capacity (EIA-860M by balancing authority, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -3844,7 +3858,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3872,7 +3886,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3900,7 +3914,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3928,7 +3942,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3956,7 +3970,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3984,7 +3998,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -4154,6 +4168,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>ISONE installed generating capacity (EIA-860M by balancing authority, net summer) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -4175,7 +4190,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -4203,7 +4218,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -4231,7 +4246,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -4287,7 +4302,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -4315,7 +4330,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -4343,7 +4358,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5202,7 +5217,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -5217,7 +5231,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -5304,7 +5317,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -5333,7 +5346,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -5362,7 +5375,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -5391,7 +5404,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -5420,7 +5433,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -5449,7 +5462,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -5478,7 +5491,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -5507,7 +5520,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -5536,7 +5549,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -5565,7 +5578,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -5594,7 +5607,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -5623,7 +5636,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -5652,7 +5665,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -5681,7 +5694,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -5710,7 +5723,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -5739,7 +5752,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -5768,7 +5781,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -5797,7 +5810,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -5826,7 +5839,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -5855,7 +5868,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -5884,7 +5897,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -5913,7 +5926,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -5942,7 +5955,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -5971,7 +5984,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -6000,7 +6013,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -6029,7 +6042,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -6058,7 +6071,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -6087,7 +6100,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -6116,7 +6129,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -6145,7 +6158,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -6174,7 +6187,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -6203,7 +6216,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -6232,7 +6245,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -6261,7 +6274,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -6290,7 +6303,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -6319,7 +6332,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -6348,7 +6361,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -6377,7 +6390,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -6406,7 +6419,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -6435,7 +6448,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -6464,7 +6477,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -6493,7 +6506,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -6522,7 +6535,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -6551,7 +6564,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -6580,7 +6593,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -6609,7 +6622,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -6638,7 +6651,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -6667,7 +6680,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -6696,7 +6709,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -6725,7 +6738,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -6754,7 +6767,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -6783,7 +6796,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -6812,7 +6825,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -6841,7 +6854,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -6870,7 +6883,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -6899,7 +6912,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -6928,7 +6941,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -6957,7 +6970,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -6986,7 +6999,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -7015,7 +7028,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -7044,7 +7057,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -7073,7 +7086,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -7102,7 +7115,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -7131,7 +7144,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -7160,7 +7173,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -7189,7 +7202,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -7218,7 +7231,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -7312,7 +7325,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -7341,7 +7354,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -7370,7 +7383,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -7399,7 +7412,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -7428,7 +7441,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -7457,7 +7470,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -7486,7 +7499,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -7515,7 +7528,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -7544,7 +7557,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -7573,7 +7586,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -7602,7 +7615,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -7631,7 +7644,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -7660,7 +7673,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -7689,7 +7702,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -7718,7 +7731,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -7747,7 +7760,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -7776,7 +7789,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -7805,7 +7818,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -7834,7 +7847,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -7863,7 +7876,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -7892,7 +7905,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -7921,7 +7934,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -7950,7 +7963,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -7979,7 +7992,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -8008,7 +8021,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -8037,7 +8050,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -8066,7 +8079,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -8095,7 +8108,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -8124,7 +8137,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -8153,7 +8166,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -8182,7 +8195,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -8211,7 +8224,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -8240,7 +8253,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -8269,7 +8282,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -8298,7 +8311,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -8327,7 +8340,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -8356,7 +8369,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -8385,7 +8398,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -8414,7 +8427,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -8443,7 +8456,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -8472,7 +8485,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -8501,7 +8514,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -8530,7 +8543,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -8559,7 +8572,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -8588,7 +8601,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -8617,7 +8630,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -8646,7 +8659,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -8675,7 +8688,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -8704,7 +8717,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -8733,7 +8746,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -8762,7 +8775,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -8791,7 +8804,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -8820,7 +8833,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -8849,7 +8862,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -8878,7 +8891,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -8907,7 +8920,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -8936,7 +8949,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -8965,7 +8978,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -8994,7 +9007,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -9023,7 +9036,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -9052,7 +9065,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -9081,7 +9094,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -9110,7 +9123,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -9139,7 +9152,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -9168,7 +9181,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -9197,7 +9210,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -9226,7 +9239,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -9320,7 +9333,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -9349,7 +9362,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -9378,7 +9391,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -9407,7 +9420,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -9436,7 +9449,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -9465,7 +9478,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -9494,7 +9507,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -9523,7 +9536,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -9552,7 +9565,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -9581,7 +9594,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -9610,7 +9623,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -9639,7 +9652,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -9668,7 +9681,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -9697,7 +9710,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -9726,7 +9739,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -9755,7 +9768,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -9784,7 +9797,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -9813,7 +9826,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -9842,7 +9855,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -9871,7 +9884,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -9900,7 +9913,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -9929,7 +9942,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -9958,7 +9971,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -9987,7 +10000,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -10016,7 +10029,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -10045,7 +10058,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -10074,7 +10087,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -10103,7 +10116,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -10132,7 +10145,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -10161,7 +10174,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -10190,7 +10203,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -10219,7 +10232,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -10248,7 +10261,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -10277,7 +10290,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -10306,7 +10319,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -10335,7 +10348,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -10364,7 +10377,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -10393,7 +10406,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -10422,7 +10435,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -10451,7 +10464,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -10480,7 +10493,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -10509,7 +10522,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -10538,7 +10551,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -10567,7 +10580,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -10596,7 +10609,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -10625,7 +10638,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -10654,7 +10667,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -10683,7 +10696,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -10712,7 +10725,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -10741,7 +10754,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -10770,7 +10783,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -10799,7 +10812,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -10828,7 +10841,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -10857,7 +10870,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -10886,7 +10899,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -10915,7 +10928,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -10944,7 +10957,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -10973,7 +10986,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -11002,7 +11015,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -11031,7 +11044,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -11060,7 +11073,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -11089,7 +11102,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -11118,7 +11131,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -11147,7 +11160,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -11176,7 +11189,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -11205,7 +11218,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -11234,7 +11247,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -11328,7 +11341,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -11357,7 +11370,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -11386,7 +11399,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -11415,7 +11428,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -11444,7 +11457,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -11473,7 +11486,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -11502,7 +11515,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -11531,7 +11544,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -11560,7 +11573,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -11589,7 +11602,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -11618,7 +11631,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -11647,7 +11660,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -11676,7 +11689,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -11705,7 +11718,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -11734,7 +11747,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -11763,7 +11776,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -11792,7 +11805,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -11821,7 +11834,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -11850,7 +11863,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -11879,7 +11892,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -11908,7 +11921,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -11937,7 +11950,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -11966,7 +11979,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -11995,7 +12008,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -12024,7 +12037,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -12053,7 +12066,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -12082,7 +12095,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -12111,7 +12124,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -12140,7 +12153,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -12169,7 +12182,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -12198,7 +12211,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -12227,7 +12240,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -12256,7 +12269,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -12285,7 +12298,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -12314,7 +12327,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -12343,7 +12356,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -12372,7 +12385,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -12401,7 +12414,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -12430,7 +12443,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -12459,7 +12472,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -12488,7 +12501,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -12517,7 +12530,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -12546,7 +12559,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -12575,7 +12588,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -12604,7 +12617,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -12633,7 +12646,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -12662,7 +12675,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -12691,7 +12704,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -12720,7 +12733,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -12749,7 +12762,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -12778,7 +12791,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -12807,7 +12820,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -12836,7 +12849,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -12865,7 +12878,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -12894,7 +12907,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -12923,7 +12936,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -12952,7 +12965,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -12981,7 +12994,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -13010,7 +13023,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -13039,7 +13052,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="C61" t="n">
@@ -13059,7 +13072,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -13088,7 +13101,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -13117,7 +13130,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -13146,7 +13159,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -13175,7 +13188,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -13204,7 +13217,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -13233,7 +13246,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -13292,7 +13305,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -13300,7 +13313,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -13308,7 +13321,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -13316,7 +13329,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -13324,7 +13337,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -13332,7 +13345,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -13340,7 +13353,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -13348,7 +13361,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -13356,7 +13369,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -13364,7 +13377,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -13372,7 +13385,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -13380,7 +13393,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -13388,7 +13401,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -13396,7 +13409,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -13404,7 +13417,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -13412,7 +13425,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -13420,7 +13433,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -13428,7 +13441,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -13436,7 +13449,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -13444,7 +13457,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -13452,7 +13465,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -13460,7 +13473,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -13468,7 +13481,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -13476,7 +13489,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -13484,7 +13497,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -13492,7 +13505,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -13500,7 +13513,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -13508,7 +13521,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -13516,7 +13529,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -13524,7 +13537,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -13532,7 +13545,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -13540,7 +13553,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -13548,7 +13561,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -13556,7 +13569,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -13564,7 +13577,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -13572,7 +13585,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -13580,7 +13593,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -13588,7 +13601,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -13596,7 +13609,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -13604,7 +13617,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -13612,7 +13625,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -13620,7 +13633,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -13628,7 +13641,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -13636,7 +13649,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -13644,7 +13657,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -13652,7 +13665,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -13660,7 +13673,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -13668,7 +13681,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -13676,7 +13689,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -13684,7 +13697,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -13692,7 +13705,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -13700,7 +13713,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -13708,7 +13721,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -13716,7 +13729,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -13724,7 +13737,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -13732,7 +13745,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -13740,7 +13753,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -13748,7 +13761,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -13756,7 +13769,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -13764,7 +13777,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -13772,7 +13785,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -13780,7 +13793,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -13788,7 +13801,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -13796,7 +13809,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -13804,7 +13817,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -13812,7 +13825,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -13820,7 +13833,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -13858,7 +13871,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -13866,7 +13879,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -13874,7 +13887,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -13882,7 +13895,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -13890,7 +13903,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -13898,7 +13911,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -13906,7 +13919,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -13914,7 +13927,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -13922,7 +13935,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -13930,7 +13943,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -13938,7 +13951,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -13946,7 +13959,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -13954,7 +13967,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -13962,7 +13975,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -13970,7 +13983,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -13978,7 +13991,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -13986,7 +13999,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -13994,7 +14007,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -14002,7 +14015,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -14010,7 +14023,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -14018,7 +14031,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -14026,7 +14039,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -14034,7 +14047,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -14042,7 +14055,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -14050,7 +14063,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -14058,7 +14071,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -14066,7 +14079,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -14074,7 +14087,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -14082,7 +14095,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -14090,7 +14103,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -14098,7 +14111,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -14106,7 +14119,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -14114,7 +14127,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -14122,7 +14135,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -14130,7 +14143,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -14138,7 +14151,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -14146,7 +14159,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -14154,7 +14167,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -14162,7 +14175,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -14170,7 +14183,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -14178,7 +14191,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -14186,7 +14199,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -14194,7 +14207,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -14202,7 +14215,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -14210,7 +14223,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -14218,7 +14231,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -14226,7 +14239,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -14234,7 +14247,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -14242,7 +14255,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -14250,7 +14263,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -14258,7 +14271,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -14266,7 +14279,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -14274,7 +14287,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -14282,7 +14295,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -14290,7 +14303,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -14298,7 +14311,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -14306,7 +14319,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -14314,7 +14327,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -14322,7 +14335,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -14330,7 +14343,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B61" t="n">
@@ -14338,7 +14351,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B62" t="n">
@@ -14346,7 +14359,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B63" t="n">
@@ -14354,7 +14367,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B64" t="n">
@@ -14362,7 +14375,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B65" t="n">
@@ -14370,7 +14383,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B66" t="n">
@@ -14378,7 +14391,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B67" t="n">
@@ -28661,7 +28674,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -28690,7 +28703,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -28719,7 +28732,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -28748,7 +28761,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -28777,7 +28790,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -28806,7 +28819,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -28835,7 +28848,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -28864,7 +28877,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -28893,7 +28906,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -28922,7 +28935,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -28951,7 +28964,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -28980,7 +28993,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -29009,7 +29022,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -29038,7 +29051,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -29067,7 +29080,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -29096,7 +29109,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -29125,7 +29138,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -29154,7 +29167,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -29183,7 +29196,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -29212,7 +29225,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -29241,7 +29254,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -29270,7 +29283,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -29299,7 +29312,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -29328,7 +29341,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -29357,7 +29370,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -29386,7 +29399,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -29415,7 +29428,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -29444,7 +29457,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -29473,7 +29486,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -29502,7 +29515,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -29531,7 +29544,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -29560,7 +29573,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -29589,7 +29602,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -29618,7 +29631,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -29647,7 +29660,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -29676,7 +29689,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -29705,7 +29718,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -29734,7 +29747,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -29763,7 +29776,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -29792,7 +29805,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -29821,7 +29834,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -29850,7 +29863,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -29879,7 +29892,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -29908,7 +29921,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -29937,7 +29950,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -29966,7 +29979,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -29995,7 +30008,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -30024,7 +30037,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -30053,7 +30066,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -30082,7 +30095,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -30111,7 +30124,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -30140,7 +30153,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -30169,7 +30182,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -30198,7 +30211,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -30227,7 +30240,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -30256,7 +30269,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -30285,7 +30298,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -30314,7 +30327,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -30343,7 +30356,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -30372,7 +30385,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -30401,7 +30414,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -30430,7 +30443,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -30459,7 +30472,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -30488,7 +30501,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -30517,7 +30530,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -30546,7 +30559,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -30575,7 +30588,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -57623,7 +57636,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -57652,7 +57665,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -57681,7 +57694,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -57710,7 +57723,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -57739,7 +57752,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -57768,7 +57781,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -57797,7 +57810,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -57826,7 +57839,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -57855,7 +57868,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -57884,7 +57897,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -57913,7 +57926,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -57942,7 +57955,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -57971,7 +57984,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -58000,7 +58013,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -58029,7 +58042,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -58058,7 +58071,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -58087,7 +58100,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -58116,7 +58129,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -58145,7 +58158,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -58174,7 +58187,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -58203,7 +58216,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -58232,7 +58245,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -58261,7 +58274,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -58290,7 +58303,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -58319,7 +58332,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -58348,7 +58361,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -58377,7 +58390,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -58406,7 +58419,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -58435,7 +58448,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -58464,7 +58477,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -58493,7 +58506,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -58522,7 +58535,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -58551,7 +58564,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -58580,7 +58593,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -58609,7 +58622,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -58638,7 +58651,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -58667,7 +58680,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -58696,7 +58709,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -58725,7 +58738,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -58754,7 +58767,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -58783,7 +58796,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -58812,7 +58825,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -58841,7 +58854,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -58870,7 +58883,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -58899,7 +58912,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -58928,7 +58941,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -58957,7 +58970,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -58986,7 +58999,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -59015,7 +59028,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -59044,7 +59057,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -59073,7 +59086,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -59102,7 +59115,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -59131,7 +59144,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -59160,7 +59173,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -59189,7 +59202,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -59218,7 +59231,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -59247,7 +59260,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -59276,7 +59289,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -59305,7 +59318,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -59334,7 +59347,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -59363,7 +59376,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -59392,7 +59405,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -59421,7 +59434,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -59450,7 +59463,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -59479,7 +59492,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -59508,7 +59521,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -59537,7 +59550,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -59631,7 +59644,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -59660,7 +59673,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -59689,7 +59702,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -59718,7 +59731,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -59747,7 +59760,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -59776,7 +59789,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -59805,7 +59818,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -59834,7 +59847,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -59863,7 +59876,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -59892,7 +59905,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -59921,7 +59934,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -59950,7 +59963,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -59979,7 +59992,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -60008,7 +60021,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -60037,7 +60050,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -60066,7 +60079,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -60095,7 +60108,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -60124,7 +60137,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -60153,7 +60166,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -60182,7 +60195,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -60211,7 +60224,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -60240,7 +60253,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -60269,7 +60282,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -60298,7 +60311,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -60327,7 +60340,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -60356,7 +60369,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -60385,7 +60398,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -60414,7 +60427,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -60443,7 +60456,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -60472,7 +60485,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -60501,7 +60514,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -60530,7 +60543,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -60559,7 +60572,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -60588,7 +60601,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -60617,7 +60630,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -60646,7 +60659,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -60675,7 +60688,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -60704,7 +60717,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -60733,7 +60746,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -60762,7 +60775,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -60791,7 +60804,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -60820,7 +60833,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -60849,7 +60862,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -60878,7 +60891,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -60907,7 +60920,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -60936,7 +60949,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -60965,7 +60978,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -60994,7 +61007,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -61023,7 +61036,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -61052,7 +61065,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -61081,7 +61094,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -61110,7 +61123,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -61139,7 +61152,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -61168,7 +61181,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -61197,7 +61210,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -61226,7 +61239,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -61255,7 +61268,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -61284,7 +61297,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -61313,7 +61326,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -61342,7 +61355,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -61371,7 +61384,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -61400,7 +61413,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -61429,7 +61442,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -61458,7 +61471,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -61487,7 +61500,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -61516,7 +61529,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -61545,7 +61558,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -61639,7 +61652,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -61668,7 +61681,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -61697,7 +61710,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -61726,7 +61739,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -61755,7 +61768,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -61784,7 +61797,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -61813,7 +61826,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -61842,7 +61855,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -61871,7 +61884,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -61900,7 +61913,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -61929,7 +61942,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -61958,7 +61971,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -61987,7 +62000,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -62016,7 +62029,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -62045,7 +62058,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -62074,7 +62087,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -62103,7 +62116,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -62132,7 +62145,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -62161,7 +62174,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -62190,7 +62203,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -62219,7 +62232,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -62248,7 +62261,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -62277,7 +62290,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -62306,7 +62319,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -62335,7 +62348,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -62364,7 +62377,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -62393,7 +62406,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -62422,7 +62435,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -62451,7 +62464,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -62480,7 +62493,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -62509,7 +62522,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -62538,7 +62551,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -62567,7 +62580,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -62596,7 +62609,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -62625,7 +62638,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -62654,7 +62667,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -62683,7 +62696,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -62712,7 +62725,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -62741,7 +62754,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -62770,7 +62783,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -62799,7 +62812,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -62828,7 +62841,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -62857,7 +62870,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -62886,7 +62899,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -62915,7 +62928,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -62944,7 +62957,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -62973,7 +62986,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -63002,7 +63015,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -63031,7 +63044,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -63060,7 +63073,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -63089,7 +63102,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -63118,7 +63131,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -63147,7 +63160,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -63176,7 +63189,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -63205,7 +63218,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -63234,7 +63247,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -63263,7 +63276,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -63292,7 +63305,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -63321,7 +63334,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -63350,7 +63363,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -63379,7 +63392,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -63408,7 +63421,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -63437,7 +63450,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -63466,7 +63479,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -63495,7 +63508,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -63524,7 +63537,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -63553,7 +63566,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -63647,7 +63660,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -63676,7 +63689,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -63705,7 +63718,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -63734,7 +63747,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -63763,7 +63776,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -63792,7 +63805,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -63821,7 +63834,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -63850,7 +63863,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -63879,7 +63892,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -63908,7 +63921,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -63937,7 +63950,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -63966,7 +63979,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -63995,7 +64008,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -64024,7 +64037,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -64053,7 +64066,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -64082,7 +64095,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -64111,7 +64124,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -64140,7 +64153,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -64169,7 +64182,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -64198,7 +64211,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -64227,7 +64240,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -64256,7 +64269,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -64285,7 +64298,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -64314,7 +64327,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -64343,7 +64356,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -64372,7 +64385,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -64401,7 +64414,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -64430,7 +64443,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -64459,7 +64472,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -64488,7 +64501,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -64517,7 +64530,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -64546,7 +64559,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -64575,7 +64588,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -64604,7 +64617,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -64633,7 +64646,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -64662,7 +64675,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -64691,7 +64704,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -64720,7 +64733,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -64749,7 +64762,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -64778,7 +64791,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -64807,7 +64820,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -64836,7 +64849,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -64865,7 +64878,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -64894,7 +64907,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -64923,7 +64936,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -64952,7 +64965,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -64981,7 +64994,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -65010,7 +65023,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -65039,7 +65052,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -65068,7 +65081,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -65097,7 +65110,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -65126,7 +65139,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -65155,7 +65168,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -65184,7 +65197,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -65213,7 +65226,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -65242,7 +65255,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -65271,7 +65284,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -65300,7 +65313,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -65329,7 +65342,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -65358,7 +65371,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -65387,7 +65400,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -65416,7 +65429,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -65445,7 +65458,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -65474,7 +65487,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -65503,7 +65516,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -65532,7 +65545,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -65561,7 +65574,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -65655,7 +65668,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -65684,7 +65697,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -65713,7 +65726,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -65742,7 +65755,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -65771,7 +65784,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -65800,7 +65813,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -65829,7 +65842,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -65858,7 +65871,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -65887,7 +65900,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -65916,7 +65929,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -65945,7 +65958,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -65974,7 +65987,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -66003,7 +66016,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -66032,7 +66045,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -66061,7 +66074,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -66090,7 +66103,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -66119,7 +66132,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -66148,7 +66161,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -66177,7 +66190,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -66206,7 +66219,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -66235,7 +66248,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -66264,7 +66277,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -66293,7 +66306,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -66322,7 +66335,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -66351,7 +66364,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -66380,7 +66393,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -66409,7 +66422,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -66438,7 +66451,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -66467,7 +66480,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -66496,7 +66509,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -66525,7 +66538,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -66554,7 +66567,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -66583,7 +66596,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -66612,7 +66625,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -66641,7 +66654,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -66670,7 +66683,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -66699,7 +66712,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -66728,7 +66741,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -66757,7 +66770,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -66786,7 +66799,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -66815,7 +66828,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -66844,7 +66857,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -66873,7 +66886,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -66902,7 +66915,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -66931,7 +66944,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -66960,7 +66973,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -66989,7 +67002,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -67018,7 +67031,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -67047,7 +67060,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -67076,7 +67089,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -67105,7 +67118,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -67134,7 +67147,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -67163,7 +67176,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -67192,7 +67205,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -67221,7 +67234,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -67250,7 +67263,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -67279,7 +67292,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -67308,7 +67321,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -67337,7 +67350,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -67366,7 +67379,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -67395,7 +67408,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -67424,7 +67437,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -67453,7 +67466,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -67482,7 +67495,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -67511,7 +67524,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -67540,7 +67553,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -67569,7 +67582,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -67663,7 +67676,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -67692,7 +67705,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -67721,7 +67734,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -67750,7 +67763,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -67779,7 +67792,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -67808,7 +67821,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -67837,7 +67850,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -67866,7 +67879,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -67895,7 +67908,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -67924,7 +67937,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -67953,7 +67966,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -67982,7 +67995,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -68011,7 +68024,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -68040,7 +68053,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -68069,7 +68082,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -68098,7 +68111,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -68127,7 +68140,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -68156,7 +68169,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -68185,7 +68198,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -68214,7 +68227,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -68243,7 +68256,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -68272,7 +68285,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -68301,7 +68314,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -68330,7 +68343,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -68359,7 +68372,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -68388,7 +68401,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -68417,7 +68430,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -68446,7 +68459,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -68475,7 +68488,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -68504,7 +68517,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -68533,7 +68546,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -68562,7 +68575,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -68591,7 +68604,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -68620,7 +68633,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -68649,7 +68662,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -68678,7 +68691,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -68707,7 +68720,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -68736,7 +68749,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -68765,7 +68778,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -68794,7 +68807,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -68823,7 +68836,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -68852,7 +68865,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -68881,7 +68894,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -68910,7 +68923,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -68939,7 +68952,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -68968,7 +68981,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -68997,7 +69010,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -69026,7 +69039,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -69055,7 +69068,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -69084,7 +69097,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -69113,7 +69126,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -69142,7 +69155,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -69171,7 +69184,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -69200,7 +69213,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -69229,7 +69242,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -69258,7 +69271,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -69287,7 +69300,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -69316,7 +69329,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -69345,7 +69358,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -69374,7 +69387,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -69403,7 +69416,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -69432,7 +69445,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -69461,7 +69474,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -69490,7 +69503,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -69519,7 +69532,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -69548,7 +69561,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -69577,7 +69590,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -69671,7 +69684,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -69700,7 +69713,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -69729,7 +69742,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -69758,7 +69771,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -69787,7 +69800,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -69816,7 +69829,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -69845,7 +69858,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -69874,7 +69887,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -69903,7 +69916,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -69932,7 +69945,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -69961,7 +69974,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -69990,7 +70003,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -70019,7 +70032,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -70048,7 +70061,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -70077,7 +70090,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -70106,7 +70119,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -70135,7 +70148,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -70164,7 +70177,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -70193,7 +70206,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -70222,7 +70235,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -70251,7 +70264,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -70280,7 +70293,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -70309,7 +70322,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -70338,7 +70351,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -70367,7 +70380,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -70396,7 +70409,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -70425,7 +70438,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -70454,7 +70467,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -70483,7 +70496,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -70512,7 +70525,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -70541,7 +70554,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -70570,7 +70583,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -70599,7 +70612,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -70628,7 +70641,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -70657,7 +70670,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -70686,7 +70699,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -70715,7 +70728,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -70744,7 +70757,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -70773,7 +70786,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -70802,7 +70815,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -70831,7 +70844,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -70860,7 +70873,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -70889,7 +70902,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -70918,7 +70931,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -70947,7 +70960,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -70976,7 +70989,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -71005,7 +71018,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -71034,7 +71047,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -71063,7 +71076,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -71092,7 +71105,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -71121,7 +71134,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -71150,7 +71163,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -71179,7 +71192,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -71208,7 +71221,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -71237,7 +71250,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -71266,7 +71279,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -71295,7 +71308,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -71324,7 +71337,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -71353,7 +71366,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -71382,7 +71395,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -71411,7 +71424,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -71440,7 +71453,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -71469,7 +71482,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -71498,7 +71511,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -71527,7 +71540,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -71556,7 +71569,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -71585,7 +71598,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
